--- a/05AnalysisOutputs/SpDynLM_Coefficients_Temp2017_w16SST_050225.xlsx
+++ b/05AnalysisOutputs/SpDynLM_Coefficients_Temp2017_w16SST_050225.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpkamakura\Documents\01GCOOS\HoustonGalvestonHeat\05AnalysisOutputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F8103EB4-55F8-4B11-AC32-C2C1A4DCA577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4714A00A-42C2-4CF6-9D60-24666A1DC3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="19932" windowHeight="11892" activeTab="2" xr2:uid="{827891E2-1AE9-462C-84E0-6AB94B5B3A8E}"/>
+    <workbookView xWindow="10572" yWindow="1236" windowWidth="12852" windowHeight="11892" firstSheet="1" activeTab="2" xr2:uid="{827891E2-1AE9-462C-84E0-6AB94B5B3A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="SpDynLM_Coefficients_Temp2017_w" sheetId="1" r:id="rId1"/>
@@ -2853,10 +2853,10 @@
       <xdr:rowOff>65478</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>99107</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>18815</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>242147</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>127566</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
